--- a/School Work/Lesson 9/openpyxl/applyToGraduate.xlsx
+++ b/School Work/Lesson 9/openpyxl/applyToGraduate.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="6">
   <si>
     <t xml:space="preserve">fName</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amountOwed</t>
   </si>
   <si>
     <t xml:space="preserve">Bill</t>
@@ -263,233 +260,199 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>15</v>
-      </c>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>16</v>
-      </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>17</v>
-      </c>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>18</v>
-      </c>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>20</v>
-      </c>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>21</v>
-      </c>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>22</v>
-      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>23</v>
-      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>24</v>
-      </c>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>25</v>
-      </c>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>26</v>
-      </c>
+      <c r="E17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>27</v>
-      </c>
+      <c r="E18" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
